--- a/site/leagues/proliga/2026_2027/xlsx/team_packs/team_pack_SCL.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/team_packs/team_pack_SCL.xlsx
@@ -957,7 +957,11 @@
           <t>S. Evans</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
@@ -1119,7 +1123,11 @@
           <t>V. Markovetskyy</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
